--- a/output/pdf_financials_xlsx/LTH.xlsx
+++ b/output/pdf_financials_xlsx/LTH.xlsx
@@ -2824,19 +2824,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.179241</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.000896</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.302389</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.841022</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.903582</v>
       </c>
     </row>
     <row r="93">
@@ -4630,7 +4630,11 @@
           <t>Warrant reserve 15</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -5224,7 +5228,11 @@
           <t>Warrant reserve 14</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -5696,7 +5704,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LTH.xlsx
+++ b/output/pdf_financials_xlsx/LTH.xlsx
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000579</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.45953</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.81994</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.341332</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.286935</v>
       </c>
     </row>
     <row r="13">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.7793679999999999</v>
+        <v>-0.778789</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-26.125384</v>
+        <v>-26.584914</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-64.324163</v>
+        <v>-65.144103</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-29.191978</v>
+        <v>-29.53331</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.912322</v>
+        <v>-4.199257</v>
       </c>
     </row>
     <row r="28">
@@ -1205,19 +1205,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.7793679999999999</v>
+        <v>-0.778789</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-26.092231</v>
+        <v>-26.551761</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-64.018913</v>
+        <v>-64.838853</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-28.834811</v>
+        <v>-29.176143</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.762806</v>
+        <v>-4.049741</v>
       </c>
     </row>
     <row r="30">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">

--- a/output/pdf_financials_xlsx/LTH.xlsx
+++ b/output/pdf_financials_xlsx/LTH.xlsx
@@ -3263,16 +3263,16 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.005352</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.034606</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.027515</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.007796</v>
       </c>
     </row>
     <row r="111">
@@ -3294,10 +3294,10 @@
         <v>-0.654087</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.046317</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.026994</v>
       </c>
     </row>
     <row r="112">
@@ -3889,10 +3889,10 @@
         <v>-0.654087</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.046317</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.026994</v>
       </c>
     </row>
     <row r="135">
@@ -3916,10 +3916,10 @@
         <v>-45.564279</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-21.047931</v>
+        <v>-21.094248</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-11.057168</v>
+        <v>-11.084162</v>
       </c>
     </row>
   </sheetData>
@@ -6408,7 +6408,11 @@
           <t>Lease accretion expense 9</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6948,7 +6952,11 @@
           <t>Purchase of equipment 8</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -7038,7 +7046,11 @@
           <t>Proceeds from private placement 14</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -7942,7 +7954,11 @@
           <t>Lease accretion expense 10</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -9270,7 +9286,11 @@
           <t>Accretion expense 9</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
